--- a/config/Creditcard.xlsx
+++ b/config/Creditcard.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11122"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11109"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/natarajankanakasabapathy/FECTech/FDL-TestDataGeneration/config/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D95BAA60-C4D1-4446-96EA-8D8B56898CD9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0EC0A152-3D93-734F-89CA-46854EC0D51B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-3100" yWindow="-21080" windowWidth="38400" windowHeight="21100" xr2:uid="{E694D55E-A215-4AD2-9B15-CC5DA999C693}"/>
+    <workbookView xWindow="-4020" yWindow="-21100" windowWidth="38400" windowHeight="21100" xr2:uid="{E694D55E-A215-4AD2-9B15-CC5DA999C693}"/>
   </bookViews>
   <sheets>
     <sheet name="Columns" sheetId="1" r:id="rId1"/>
